--- a/filer/80673612_scan.xlsx
+++ b/filer/80673612_scan.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-mellem · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/80673612_scan.xlsx
+++ b/filer/80673612_scan.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_80673612" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_80673612" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_80673612" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_80673612" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -662,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1435,35 +1436,35 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
@@ -2769,35 +2770,35 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
@@ -4151,19 +4152,19 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
@@ -4269,19 +4270,19 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
@@ -4578,6 +4579,148 @@
       </c>
       <c r="F94" s="13">
         <f>IFERROR($F$31/($F$56+$F$63)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B97" s="17">
+        <f>'pengestrom_raw_80673612'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C97" s="17">
+        <f>'pengestrom_raw_80673612'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D97" s="17">
+        <f>'pengestrom_raw_80673612'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E97" s="17">
+        <f>'pengestrom_raw_80673612'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F97" s="17">
+        <f>'pengestrom_raw_80673612'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B98" s="17">
+        <f>'pengestrom_raw_80673612'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C98" s="17">
+        <f>'pengestrom_raw_80673612'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D98" s="17">
+        <f>'pengestrom_raw_80673612'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E98" s="17">
+        <f>'pengestrom_raw_80673612'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F98" s="17">
+        <f>'pengestrom_raw_80673612'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B99" s="17">
+        <f>'pengestrom_raw_80673612'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C99" s="17">
+        <f>'pengestrom_raw_80673612'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D99" s="17">
+        <f>'pengestrom_raw_80673612'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E99" s="17">
+        <f>'pengestrom_raw_80673612'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F99" s="17">
+        <f>'pengestrom_raw_80673612'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B100" s="17">
+        <f>'pengestrom_raw_80673612'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C100" s="17">
+        <f>'pengestrom_raw_80673612'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D100" s="17">
+        <f>'pengestrom_raw_80673612'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E100" s="17">
+        <f>'pengestrom_raw_80673612'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F100" s="17">
+        <f>'pengestrom_raw_80673612'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B101">
+        <f>IF(ABS(('pengestrom_raw_80673612'!$B$2+'pengestrom_raw_80673612'!$B$3+'pengestrom_raw_80673612'!$B$4)-'pengestrom_raw_80673612'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_80673612'!$B$2+'pengestrom_raw_80673612'!$B$3+'pengestrom_raw_80673612'!$B$4)-'pengestrom_raw_80673612'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C101">
+        <f>IF(ABS(('pengestrom_raw_80673612'!$C$2+'pengestrom_raw_80673612'!$C$3+'pengestrom_raw_80673612'!$C$4)-'pengestrom_raw_80673612'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_80673612'!$C$2+'pengestrom_raw_80673612'!$C$3+'pengestrom_raw_80673612'!$C$4)-'pengestrom_raw_80673612'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D101">
+        <f>IF(ABS(('pengestrom_raw_80673612'!$D$2+'pengestrom_raw_80673612'!$D$3+'pengestrom_raw_80673612'!$D$4)-'pengestrom_raw_80673612'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_80673612'!$D$2+'pengestrom_raw_80673612'!$D$3+'pengestrom_raw_80673612'!$D$4)-'pengestrom_raw_80673612'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E101">
+        <f>IF(ABS(('pengestrom_raw_80673612'!$E$2+'pengestrom_raw_80673612'!$E$3+'pengestrom_raw_80673612'!$E$4)-'pengestrom_raw_80673612'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_80673612'!$E$2+'pengestrom_raw_80673612'!$E$3+'pengestrom_raw_80673612'!$E$4)-'pengestrom_raw_80673612'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F101">
+        <f>IF(ABS(('pengestrom_raw_80673612'!$F$2+'pengestrom_raw_80673612'!$F$3+'pengestrom_raw_80673612'!$F$4)-'pengestrom_raw_80673612'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_80673612'!$F$2+'pengestrom_raw_80673612'!$F$3+'pengestrom_raw_80673612'!$F$4)-'pengestrom_raw_80673612'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4610,353 +4753,353 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsomkostninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>43224</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>75873</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>52019</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>31064</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>44876</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>54264</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Salgs- og distributionsomkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>21802</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>26983</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>25379</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>24645</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>26429</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>27637</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Administrationsomkostninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>12315</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>17351</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>16466</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>19296</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>21534</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>22151</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>749</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F8" s="17" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>8359</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>31524</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>10175</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>-12881</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>-3088</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>4471</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>4727</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>323</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>674</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>664</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>338</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>309</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>509</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>1232</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>836</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>1067</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>628</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>1603</v>
       </c>
+      <c r="F12" s="17" t="n">
+        <v>2502</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>27528</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>46170</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>23988</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>-7153</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>1475</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>7257</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>1684</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>6583</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>2299</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>-2815</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>-723</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>515</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>25844</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>39587</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>21689</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>-4338</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>2198</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>6742</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>102</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>126</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>120</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>107</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>98</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>5247</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>4719</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>1831</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>462</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>2585</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>1745</v>
       </c>
     </row>
   </sheetData>
@@ -4988,1095 +5131,1093 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n">
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n">
         <v>750</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>520</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>10392</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>9802</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>10123</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>9858</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>9327</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>8796</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>4579</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>4968</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>3870</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>2700</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>1626</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>2308</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>1915</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>3161</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>2074</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>998</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>2263</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>1422</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>2360</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>1904</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>1425</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>1050</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>736</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>449</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>19247</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>19834</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>17492</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>14607</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>13952</v>
       </c>
+      <c r="F8" s="17" t="n">
+        <v>12974</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>14193</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>717</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>768</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>858</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>852</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>851</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>851</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>56463</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>45793</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>46059</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>40745</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>49360</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>43734</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>75709</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>65627</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>63551</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>55352</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>64062</v>
       </c>
+      <c r="F12" s="17" t="n">
+        <v>57228</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>12348</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>31701</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>29329</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>22573</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>27079</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>27956</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>6405</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>7155</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>7196</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>8674</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>7935</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>7972</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>14168</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>24519</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>37011</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>35611</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>33732</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>38552</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>32921</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>63375</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>73536</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>66858</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>68747</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>74480</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>18965</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>33119</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>25329</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>25076</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>24017</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>28227</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>2343</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>0</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>2321</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>728</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>2745</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>990</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>1604</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>1356</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>1473</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>236</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>176</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>522</v>
       </c>
+      <c r="F20" s="17" t="n">
+        <v>397</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n">
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n">
         <v>2104</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>2912</v>
       </c>
+      <c r="F21" s="17" t="n">
+        <v>2480</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="16" t="n">
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n">
         <v>94</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>534</v>
       </c>
+      <c r="F23" s="17" t="n">
+        <v>267</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
-        <v>28830</v>
-      </c>
-      <c r="C24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>40981</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>26347</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>34743</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>33480</v>
       </c>
+      <c r="F24" s="17" t="n">
+        <v>34182</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
-        <v>1545</v>
-      </c>
-      <c r="C26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>24104</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>18311</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>25798</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>32459</v>
       </c>
+      <c r="F26" s="17" t="n">
+        <v>22306</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
-        <v>63297</v>
-      </c>
-      <c r="C27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>128461</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>118195</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>127399</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>134685</v>
       </c>
+      <c r="F27" s="17" t="n">
+        <v>130968</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
-        <v>139006</v>
-      </c>
-      <c r="C28" s="16" t="n">
+      <c r="B28" s="17" t="n">
         <v>194088</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="C28" s="17" t="n">
         <v>181746</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>182751</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>198748</v>
       </c>
+      <c r="F28" s="17" t="n">
+        <v>188196</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="17" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
-        <v>47549</v>
-      </c>
-      <c r="C30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>55200</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>56809</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>34732</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>43348</v>
       </c>
+      <c r="F30" s="17" t="n">
+        <v>37722</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
-        <v>36</v>
-      </c>
-      <c r="C32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>131</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
-        <v>32771</v>
-      </c>
-      <c r="C34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>64913</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>89365</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>105227</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="E34" s="17" t="n">
         <v>92146</v>
       </c>
+      <c r="F34" s="17" t="n">
+        <v>87989</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
-        <v>90857</v>
-      </c>
-      <c r="C35" s="16" t="n">
+      <c r="B35" s="17" t="n">
         <v>125244</v>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="C35" s="17" t="n">
         <v>147174</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="D35" s="17" t="n">
         <v>140959</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="E35" s="17" t="n">
         <v>146494</v>
       </c>
+      <c r="F35" s="17" t="n">
+        <v>136711</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
-        <v>529</v>
-      </c>
-      <c r="C36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>607</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>727</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>2104</v>
       </c>
+      <c r="F36" s="17" t="n">
+        <v>2912</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
-        <v>2256</v>
-      </c>
-      <c r="C37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>2774</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>2934</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>1866</v>
       </c>
+      <c r="F37" s="17" t="n">
+        <v>1786</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
-        <v>4538</v>
-      </c>
-      <c r="C39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>4203</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
-        <v>1942</v>
-      </c>
-      <c r="C40" s="16" t="n">
+      <c r="B40" s="17" t="n">
         <v>2073</v>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="C40" s="17" t="n">
         <v>1182</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <v>193</v>
       </c>
-      <c r="F40" s="16" t="n">
+      <c r="E40" s="17" t="n">
         <v>1908</v>
       </c>
+      <c r="F40" s="17" t="n">
+        <v>269</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n">
-        <v>4328</v>
-      </c>
-      <c r="C41" s="16" t="n">
+      <c r="B41" s="17" t="n">
         <v>4376</v>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="C41" s="17" t="n">
         <v>4468</v>
       </c>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
-        <v>13752</v>
-      </c>
-      <c r="C42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>10652</v>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>5650</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="D42" s="17" t="n">
         <v>4770</v>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="E42" s="17" t="n">
         <v>6481</v>
       </c>
+      <c r="F42" s="17" t="n">
+        <v>4841</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
-        <v>2540</v>
-      </c>
-      <c r="C44" s="16" t="n">
+      <c r="B44" s="17" t="n">
         <v>1262</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="C44" s="17" t="n">
         <v>369</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="D44" s="17" t="n">
         <v>302</v>
       </c>
-      <c r="F44" s="16" t="n">
+      <c r="E44" s="17" t="n">
         <v>221</v>
       </c>
+      <c r="F44" s="17" t="n">
+        <v>951</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
-        <v>4819</v>
-      </c>
-      <c r="C45" s="16" t="n">
+      <c r="B45" s="17" t="n">
         <v>12972</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="C45" s="17" t="n">
         <v>3395</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>8988</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="E45" s="17" t="n">
         <v>25002</v>
       </c>
+      <c r="F45" s="17" t="n">
+        <v>22103</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
-        <v>10766</v>
-      </c>
-      <c r="C47" s="16" t="n">
+      <c r="B47" s="17" t="n">
         <v>19187</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>7403</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>12231</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>6616</v>
       </c>
+      <c r="F47" s="17" t="n">
+        <v>13359</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
+      <c r="B48" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C48" s="16" t="n">
+      <c r="C48" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="D48" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="E48" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F48" s="16" t="n">
+      <c r="F48" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
-        <v>376</v>
-      </c>
-      <c r="C50" s="16" t="n">
+      <c r="B50" s="17" t="n">
         <v>6573</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>2202</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="16" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="F50" s="17" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n"/>
+      <c r="F51" s="17" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
-        <v>13613</v>
-      </c>
-      <c r="C52" s="16" t="n">
+      <c r="B52" s="17" t="n">
         <v>14901</v>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="C52" s="17" t="n">
         <v>12572</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="D52" s="17" t="n">
         <v>13292</v>
       </c>
-      <c r="F52" s="16" t="n">
+      <c r="E52" s="17" t="n">
         <v>11934</v>
       </c>
+      <c r="F52" s="17" t="n">
+        <v>8223</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
-        <v>26</v>
-      </c>
-      <c r="C53" s="16" t="n">
+      <c r="B53" s="17" t="n">
         <v>401</v>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="C53" s="17" t="n">
         <v>47</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="D53" s="17" t="n">
         <v>209</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="E53" s="17" t="n">
         <v>133</v>
       </c>
+      <c r="F53" s="17" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n">
-        <v>32141</v>
-      </c>
-      <c r="C54" s="16" t="n">
+      <c r="B54" s="17" t="n">
         <v>55418</v>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="C54" s="17" t="n">
         <v>25988</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="D54" s="17" t="n">
         <v>35022</v>
       </c>
-      <c r="F54" s="16" t="n">
+      <c r="E54" s="17" t="n">
         <v>43907</v>
       </c>
+      <c r="F54" s="17" t="n">
+        <v>44857</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
-        <v>45893</v>
-      </c>
-      <c r="C55" s="16" t="n">
+      <c r="B55" s="17" t="n">
         <v>66070</v>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="C55" s="17" t="n">
         <v>31637</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>39792</v>
       </c>
-      <c r="F55" s="16" t="n">
+      <c r="E55" s="17" t="n">
         <v>50388</v>
       </c>
+      <c r="F55" s="17" t="n">
+        <v>49698</v>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B56" s="16" t="n">
-        <v>139006</v>
-      </c>
-      <c r="C56" s="16" t="n">
+      <c r="B56" s="17" t="n">
         <v>194088</v>
       </c>
-      <c r="D56" s="16" t="n">
+      <c r="C56" s="17" t="n">
         <v>181746</v>
       </c>
-      <c r="E56" s="16" t="n">
+      <c r="D56" s="17" t="n">
         <v>182751</v>
       </c>
-      <c r="F56" s="16" t="n">
+      <c r="E56" s="17" t="n">
         <v>198748</v>
+      </c>
+      <c r="F56" s="17" t="n">
+        <v>188196</v>
       </c>
     </row>
   </sheetData>
@@ -6085,6 +6226,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>-602</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>-5340</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>-6923</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>-7788</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>11016</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>16101</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>9873</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-3375</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-1144</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-16554</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>4537</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>17824</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-13808</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6115,13 +6378,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6811,7 +7074,7 @@
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B39" s="22" t="n"/>
@@ -6929,7 +7192,7 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B46" s="22" t="n"/>
@@ -7105,7 +7368,7 @@
     <row r="57">
       <c r="A57" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B57" s="29" t="n"/>
@@ -7283,7 +7546,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7328,27 +7591,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7373,16 +7636,16 @@
           <t>fsa:ExchangeRateAdjustmentsOtherFinanceExpenses</t>
         </is>
       </c>
-      <c r="D3" s="35" t="n"/>
+      <c r="D3" s="35" t="n">
+        <v>8</v>
+      </c>
       <c r="E3" s="35" t="n">
-        <v>8</v>
+        <v>217</v>
       </c>
       <c r="F3" s="35" t="n">
-        <v>217</v>
-      </c>
-      <c r="G3" s="35" t="n">
         <v>0</v>
       </c>
+      <c r="G3" s="35" t="n"/>
       <c r="H3" s="35" t="n"/>
       <c r="I3" s="36" t="inlineStr">
         <is>
@@ -7406,16 +7669,16 @@
           <t>fsa:Loans</t>
         </is>
       </c>
-      <c r="D4" s="38" t="n"/>
+      <c r="D4" s="38" t="n">
+        <v>-50</v>
+      </c>
       <c r="E4" s="38" t="n">
-        <v>-50</v>
+        <v>-90</v>
       </c>
       <c r="F4" s="38" t="n">
-        <v>-90</v>
-      </c>
-      <c r="G4" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="G4" s="38" t="n"/>
       <c r="H4" s="38" t="n"/>
       <c r="I4" s="39" t="inlineStr">
         <is>
@@ -7442,9 +7705,11 @@
       <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n"/>
       <c r="F5" s="35" t="n"/>
-      <c r="G5" s="35" t="n"/>
+      <c r="G5" s="35" t="n">
+        <v>1715</v>
+      </c>
       <c r="H5" s="35" t="n">
-        <v>1715</v>
+        <v>0</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -7468,19 +7733,19 @@
           <t>fsa:ReductionOfLeaseCommitments</t>
         </is>
       </c>
-      <c r="D6" s="38" t="n"/>
+      <c r="D6" s="38" t="n">
+        <v>-1810</v>
+      </c>
       <c r="E6" s="38" t="n">
-        <v>-1810</v>
+        <v>-1236</v>
       </c>
       <c r="F6" s="38" t="n">
-        <v>-1236</v>
+        <v>-741</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>-741</v>
-      </c>
-      <c r="H6" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="H6" s="38" t="n"/>
       <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7503,16 +7768,16 @@
           <t>fsa:RepaymentOfMortgageDebt</t>
         </is>
       </c>
-      <c r="D7" s="35" t="n"/>
+      <c r="D7" s="35" t="n">
+        <v>-335</v>
+      </c>
       <c r="E7" s="35" t="n">
-        <v>-335</v>
+        <v>-4203</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>-4203</v>
-      </c>
-      <c r="G7" s="35" t="n">
         <v>0</v>
       </c>
+      <c r="G7" s="35" t="n"/>
       <c r="H7" s="35" t="n"/>
       <c r="I7" s="36" t="inlineStr">
         <is>
@@ -7536,13 +7801,13 @@
           <t>fsa:ShorttermPayablesToAssociates</t>
         </is>
       </c>
-      <c r="D8" s="38" t="n"/>
+      <c r="D8" s="38" t="n">
+        <v>122</v>
+      </c>
       <c r="E8" s="38" t="n">
-        <v>122</v>
-      </c>
-      <c r="F8" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="F8" s="38" t="n"/>
       <c r="G8" s="38" t="n"/>
       <c r="H8" s="38" t="n"/>
       <c r="I8" s="39" t="inlineStr">
